--- a/碳盤查試算表_v5.xlsx
+++ b/碳盤查試算表_v5.xlsx
@@ -2742,7 +2742,7 @@
     </r>
   </si>
   <si>
-    <t xml:space="preserve">附表四對化石燃料所排放之甲烷另訂 GWP=30（一般甲烷為28）。本表燃料類一律採 30，此為附表四註1之明文規定。</t>
+    <t xml:space="preserve">附表四註1對化石燃料所排放之甲烷另訂 GWP=30（一般甲烷為28），但環境部平台已公告「修正甲烷及石化甲烷GWP適用情形」，燃料燃燒（含固定及移動設備）一律改採甲烷 28。本表已依此辦理，計算一律用 28，不使用 30；石化甲烷一列僅保留供對照。詳見第 0 條與「GWP表」分頁。</t>
   </si>
   <si>
     <r>

--- a/碳盤查試算表_v5.xlsx
+++ b/碳盤查試算表_v5.xlsx
@@ -609,7 +609,7 @@
     <t xml:space="preserve">GM01</t>
   </si>
   <si>
-    <t xml:space="preserve">0020</t>
+    <t xml:space="preserve">B001</t>
   </si>
   <si>
     <t xml:space="preserve">050002</t>
@@ -621,7 +621,7 @@
     <t xml:space="preserve">TW-F-NG-S</t>
   </si>
   <si>
-    <t xml:space="preserve">設備代碼無「瓦斯爐」，暫歸燃氣鍋爐，須於報告說明</t>
+    <t xml:space="preserve">採官方附表六 B001 燃氣台爐。前版暫歸 0020 燃氣鍋爐（工業鍋爐），係僅查閱代碼表子集所致，全量匯入後更正</t>
   </si>
   <si>
     <t xml:space="preserve">S05</t>
@@ -2175,7 +2175,7 @@
     <t xml:space="preserve">其他未分類製程</t>
   </si>
   <si>
-    <t xml:space="preserve">燃氣鍋爐</t>
+    <t xml:space="preserve">燃氣台爐</t>
   </si>
   <si>
     <t xml:space="preserve">交通運輸活動</t>
@@ -4901,7 +4901,7 @@
       </c>
       <c r="H7" s="11" t="str">
         <f aca="false">IFERROR(INDEX(代碼表!$E$5:$E$13,MATCH($G7,代碼表!$D$5:$D$13,0)),"")</f>
-        <v>燃氣鍋爐</v>
+        <v>燃氣台爐</v>
       </c>
       <c r="I7" s="9" t="s">
         <v>106</v>
